--- a/stock.xlsx
+++ b/stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08.ubuntu_ws\ediedone.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525971C2-0C67-4B27-B660-C962AB52FD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5566524A-9D85-4539-B0CE-0C8F64401C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{69258048-4F87-458D-9BA6-694171A7783B}"/>
   </bookViews>
@@ -798,6 +798,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -813,22 +822,13 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1211,16 +1211,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3">
-        <v>3.2639999999999998</v>
+        <v>2.9910000000000001</v>
       </c>
       <c r="B2" s="4">
-        <v>-1.29E-2</v>
+        <v>-8.3699999999999997E-2</v>
       </c>
       <c r="C2" s="5">
-        <v>265.88</v>
+        <v>223.92</v>
       </c>
       <c r="D2" s="30">
-        <v>0.74199999999999999</v>
+        <v>0.71930000000000005</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -1232,32 +1232,32 @@
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="37">
-        <v>3.54</v>
-      </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
+      <c r="B5" s="32">
+        <v>3.2149999999999999</v>
+      </c>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="33">
-        <v>-1.44E-2</v>
-      </c>
-      <c r="G5" s="34"/>
+      <c r="F5" s="36">
+        <v>-9.1700000000000004E-2</v>
+      </c>
+      <c r="G5" s="37"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="11" t="s">
@@ -1283,84 +1283,84 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="40">
-        <v>4.4999999999999998E-2</v>
+      <c r="B7" s="34">
+        <v>4.1799999999999997E-2</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>62</v>
       </c>
       <c r="D7" s="7">
-        <v>2.2499999999999999E-2</v>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="E7" s="8">
-        <v>942.3</v>
+        <v>801.4</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="42"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="28" t="s">
         <v>61</v>
       </c>
       <c r="D8" s="7">
-        <v>1.2500000000000001E-2</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="E8" s="8">
-        <v>942.3</v>
+        <v>801.4</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="42"/>
-      <c r="B9" s="40"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="28" t="s">
         <v>60</v>
       </c>
       <c r="D9" s="7">
-        <v>0.01</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="E9" s="8">
-        <v>942.3</v>
+        <v>801.4</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="40">
-        <v>9.7000000000000003E-3</v>
+      <c r="B10" s="34">
+        <v>1.09E-2</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7">
-        <v>8.0000000000000004E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="E10" s="8">
-        <v>5.0999999999999996</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="42"/>
-      <c r="B11" s="40"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="7">
-        <v>8.8999999999999999E-3</v>
+        <v>0.01</v>
       </c>
       <c r="E11" s="8">
-        <v>246.1</v>
+        <v>265.64</v>
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
@@ -1370,16 +1370,16 @@
         <v>6</v>
       </c>
       <c r="B12" s="4">
-        <v>5.4000000000000003E-3</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="7">
-        <v>5.4000000000000003E-3</v>
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="E12" s="8">
-        <v>1646</v>
+        <v>1699</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -1389,65 +1389,65 @@
         <v>8</v>
       </c>
       <c r="B13" s="4">
-        <v>5.21E-2</v>
+        <v>5.2600000000000001E-2</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="7">
-        <v>5.21E-2</v>
+        <v>5.2600000000000001E-2</v>
       </c>
       <c r="E13" s="8">
-        <v>1822</v>
+        <v>1723.5</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="40">
-        <v>0.3926</v>
+      <c r="B14" s="34">
+        <v>0.36509999999999998</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>59</v>
       </c>
       <c r="D14" s="7">
-        <v>0.1273</v>
+        <v>0.11840000000000001</v>
       </c>
       <c r="E14" s="8">
-        <v>54300</v>
+        <v>47200</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="38"/>
-      <c r="B15" s="40"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="31" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="7">
-        <v>0.1804</v>
+        <v>0.1678</v>
       </c>
       <c r="E15" s="8">
-        <v>54300</v>
+        <v>47200</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="38"/>
-      <c r="B16" s="40"/>
+      <c r="A16" s="40"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="31" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="7">
-        <v>8.4900000000000003E-2</v>
+        <v>7.8899999999999998E-2</v>
       </c>
       <c r="E16" s="8">
-        <v>54300</v>
+        <v>47200</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1457,32 +1457,32 @@
         <v>13</v>
       </c>
       <c r="B17" s="4">
-        <v>2.9899999999999999E-2</v>
+        <v>2.7099999999999999E-2</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="7">
-        <v>2.9899999999999999E-2</v>
+        <v>2.7099999999999999E-2</v>
       </c>
       <c r="E17" s="8">
-        <v>246.4</v>
+        <v>209.75</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="40">
-        <v>4.2700000000000002E-2</v>
+      <c r="B18" s="34">
+        <v>4.4400000000000002E-2</v>
       </c>
       <c r="C18" s="28" t="s">
         <v>56</v>
       </c>
       <c r="D18" s="7">
-        <v>3.0499999999999999E-2</v>
+        <v>3.27E-2</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>4</v>
@@ -1491,13 +1491,13 @@
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="41"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="31" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="7">
-        <v>1.2200000000000001E-2</v>
+        <v>1.17E-2</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>4</v>
@@ -1510,16 +1510,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="4">
-        <v>1.38E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="7">
-        <v>1.38E-2</v>
+        <v>1.46E-2</v>
       </c>
       <c r="E20" s="8">
-        <v>780.1</v>
+        <v>759.2</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -1529,50 +1529,50 @@
         <v>19</v>
       </c>
       <c r="B21" s="4">
-        <v>3.5799999999999998E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="7">
-        <v>3.5799999999999998E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="E21" s="8">
-        <v>265.2</v>
+        <v>284.32</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="40">
-        <v>2.7799999999999998E-2</v>
+      <c r="B22" s="34">
+        <v>3.1800000000000002E-2</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>22</v>
       </c>
       <c r="D22" s="7">
-        <v>1.55E-2</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="E22" s="8">
-        <v>674.6</v>
+        <v>734.05</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="41"/>
-      <c r="B23" s="40"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="34"/>
       <c r="C23" s="31" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="7">
-        <v>1.23E-2</v>
+        <v>1.37E-2</v>
       </c>
       <c r="E23" s="8">
-        <v>5834</v>
+        <v>5977</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -1582,16 +1582,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="4">
-        <v>8.6E-3</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="7">
-        <v>8.6E-3</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="E24" s="8">
-        <v>171.9</v>
+        <v>171.15</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
@@ -1601,16 +1601,16 @@
         <v>26</v>
       </c>
       <c r="B25" s="4">
-        <v>3.8999999999999998E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="7">
-        <v>3.8999999999999998E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="E25" s="8">
-        <v>1466</v>
+        <v>1388</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
@@ -1620,16 +1620,16 @@
         <v>28</v>
       </c>
       <c r="B26" s="4">
-        <v>2.8999999999999998E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="7">
-        <v>2.8999999999999998E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="E26" s="8">
-        <v>62.64</v>
+        <v>61.48</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1642,32 +1642,32 @@
       <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="37">
-        <v>2.423</v>
-      </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
+      <c r="B29" s="32">
+        <v>2.327</v>
+      </c>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
       <c r="E29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F29" s="35">
-        <v>-5.5999999999999999E-3</v>
-      </c>
-      <c r="G29" s="36"/>
+      <c r="F29" s="38">
+        <v>-3.9699999999999999E-2</v>
+      </c>
+      <c r="G29" s="39"/>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="11" t="s">
@@ -1706,7 +1706,7 @@
         <v>1.4E-2</v>
       </c>
       <c r="E31" s="8">
-        <v>10.85</v>
+        <v>10.16</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
@@ -1716,32 +1716,32 @@
         <v>31</v>
       </c>
       <c r="B32" s="7">
-        <v>7.9000000000000008E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="C32" s="26" t="s">
         <v>32</v>
       </c>
       <c r="D32" s="7">
-        <v>7.9000000000000008E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
       <c r="E32" s="8">
-        <v>138.52000000000001</v>
+        <v>115.71</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="39">
-        <v>1.5599999999999999E-2</v>
+      <c r="B33" s="41">
+        <v>1.55E-2</v>
       </c>
       <c r="C33" s="27" t="s">
         <v>58</v>
       </c>
       <c r="D33" s="7">
-        <v>7.1000000000000004E-3</v>
+        <v>7.6E-3</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>4</v>
@@ -1750,13 +1750,13 @@
       <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39"/>
+      <c r="A34" s="40"/>
+      <c r="B34" s="41"/>
       <c r="C34" s="27" t="s">
         <v>55</v>
       </c>
       <c r="D34" s="7">
-        <v>8.5000000000000006E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>4</v>
@@ -1765,11 +1765,11 @@
       <c r="G34" s="10"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="38" t="s">
+      <c r="A35" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="39">
-        <v>3.4299999999999997E-2</v>
+      <c r="B35" s="41">
+        <v>3.1099999999999999E-2</v>
       </c>
       <c r="C35" s="26" t="s">
         <v>35</v>
@@ -1778,22 +1778,22 @@
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="E35" s="8">
-        <v>1886.63</v>
+        <v>1976.75</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="38"/>
-      <c r="B36" s="39"/>
+      <c r="A36" s="40"/>
+      <c r="B36" s="41"/>
       <c r="C36" s="26" t="s">
         <v>36</v>
       </c>
       <c r="D36" s="7">
-        <v>3.3700000000000001E-2</v>
+        <v>3.0499999999999999E-2</v>
       </c>
       <c r="E36" s="8">
-        <v>434.14</v>
+        <v>366.9</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
@@ -1806,11 +1806,11 @@
       <c r="E37" s="17"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="35"/>
       <c r="D38" s="25"/>
       <c r="E38" s="25"/>
     </row>
@@ -1836,18 +1836,13 @@
       </c>
       <c r="C40" s="9">
         <f>A2*B40</f>
-        <v>502671.78796799999</v>
+        <v>460628.46746700001</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A38:C38"/>
@@ -1864,6 +1859,11 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0" right="0" top="0.39370000000000011" bottom="0.39370000000000011" header="0" footer="0"/>

--- a/stock.xlsx
+++ b/stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08.ubuntu_ws\ediedone.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5566524A-9D85-4539-B0CE-0C8F64401C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09399B32-A8E7-417C-BCCF-8A1606ED5751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{69258048-4F87-458D-9BA6-694171A7783B}"/>
   </bookViews>
@@ -104,9 +104,6 @@
     <t>家用电器</t>
   </si>
   <si>
-    <t>思摩尔国际</t>
-  </si>
-  <si>
     <t>美的集团</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
   </si>
   <si>
     <t>食物饮品</t>
-  </si>
-  <si>
-    <t>海天味业</t>
   </si>
   <si>
     <t>古井贡B</t>
@@ -375,6 +369,14 @@
       </rPr>
       <t>F</t>
     </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>海天味业</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>思摩尔国际</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -798,37 +800,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1196,31 +1198,31 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3">
-        <v>2.9910000000000001</v>
+        <v>3.032</v>
       </c>
       <c r="B2" s="4">
-        <v>-8.3699999999999997E-2</v>
+        <v>1.38E-2</v>
       </c>
       <c r="C2" s="5">
-        <v>223.92</v>
+        <v>230.26</v>
       </c>
       <c r="D2" s="30">
-        <v>0.71930000000000005</v>
+        <v>0.72219999999999995</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -1232,135 +1234,135 @@
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
+      <c r="A4" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="32">
-        <v>3.2149999999999999</v>
-      </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
+      <c r="B5" s="37">
+        <v>3.27</v>
+      </c>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="36">
-        <v>-9.1700000000000004E-2</v>
-      </c>
-      <c r="G5" s="37"/>
+        <v>52</v>
+      </c>
+      <c r="F5" s="33">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="G5" s="34"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="34">
-        <v>4.1799999999999997E-2</v>
+      <c r="B7" s="40">
+        <v>3.9600000000000003E-2</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D7" s="7">
-        <v>2.0899999999999998E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="E7" s="8">
-        <v>801.4</v>
+        <v>771.8</v>
       </c>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="33"/>
-      <c r="B8" s="34"/>
+      <c r="A8" s="42"/>
+      <c r="B8" s="40"/>
       <c r="C8" s="28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7">
-        <v>1.1599999999999999E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E8" s="8">
-        <v>801.4</v>
+        <v>771.8</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="33"/>
-      <c r="B9" s="34"/>
+      <c r="A9" s="42"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D9" s="7">
-        <v>9.2999999999999992E-3</v>
+        <v>8.8000000000000005E-3</v>
       </c>
       <c r="E9" s="8">
-        <v>801.4</v>
+        <v>771.8</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="34">
-        <v>1.09E-2</v>
+      <c r="B10" s="40">
+        <v>1.06E-2</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7">
-        <v>8.9999999999999998E-4</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="E10" s="8">
-        <v>5.0199999999999996</v>
+        <v>4.72</v>
       </c>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="33"/>
-      <c r="B11" s="34"/>
+      <c r="A11" s="42"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="31" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="7">
-        <v>0.01</v>
+        <v>9.7999999999999997E-3</v>
       </c>
       <c r="E11" s="8">
-        <v>265.64</v>
+        <v>262.58999999999997</v>
       </c>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
@@ -1379,7 +1381,7 @@
         <v>6.1000000000000004E-3</v>
       </c>
       <c r="E12" s="8">
-        <v>1699</v>
+        <v>1734</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -1389,65 +1391,65 @@
         <v>8</v>
       </c>
       <c r="B13" s="4">
-        <v>5.2600000000000001E-2</v>
+        <v>4.8599999999999997E-2</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="7">
-        <v>5.2600000000000001E-2</v>
+        <v>4.8599999999999997E-2</v>
       </c>
       <c r="E13" s="8">
-        <v>1723.5</v>
+        <v>1606.6</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="34">
-        <v>0.36509999999999998</v>
+      <c r="B14" s="40">
+        <v>0.38219999999999998</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D14" s="7">
-        <v>0.11840000000000001</v>
+        <v>0.1241</v>
       </c>
       <c r="E14" s="8">
-        <v>47200</v>
+        <v>49900</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="40"/>
-      <c r="B15" s="34"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="31" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="7">
-        <v>0.1678</v>
+        <v>0.1757</v>
       </c>
       <c r="E15" s="8">
-        <v>47200</v>
+        <v>49900</v>
       </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="40"/>
-      <c r="B16" s="34"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="31" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="7">
-        <v>7.8899999999999998E-2</v>
+        <v>8.2400000000000001E-2</v>
       </c>
       <c r="E16" s="8">
-        <v>47200</v>
+        <v>49900</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1457,32 +1459,32 @@
         <v>13</v>
       </c>
       <c r="B17" s="4">
-        <v>2.7099999999999999E-2</v>
+        <v>2.4899999999999999E-2</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="7">
-        <v>2.7099999999999999E-2</v>
+        <v>2.4899999999999999E-2</v>
       </c>
       <c r="E17" s="8">
-        <v>209.75</v>
+        <v>194.41</v>
       </c>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="34">
-        <v>4.4400000000000002E-2</v>
+      <c r="B18" s="40">
+        <v>4.2099999999999999E-2</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" s="7">
-        <v>3.27E-2</v>
+        <v>3.1E-2</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>4</v>
@@ -1491,13 +1493,13 @@
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="42"/>
-      <c r="B19" s="34"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="31" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="7">
-        <v>1.17E-2</v>
+        <v>1.11E-2</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>4</v>
@@ -1510,16 +1512,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="4">
-        <v>1.46E-2</v>
+        <v>1.3899999999999999E-2</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="7">
-        <v>1.46E-2</v>
+        <v>1.3899999999999999E-2</v>
       </c>
       <c r="E20" s="8">
-        <v>759.2</v>
+        <v>728.3</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -1529,107 +1531,107 @@
         <v>19</v>
       </c>
       <c r="B21" s="4">
-        <v>4.1000000000000002E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="7">
-        <v>4.1000000000000002E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="E21" s="8">
-        <v>284.32</v>
+        <v>285.32</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="34">
-        <v>3.1800000000000002E-2</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>22</v>
+      <c r="B22" s="40">
+        <v>3.1099999999999999E-2</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="D22" s="7">
-        <v>1.8100000000000002E-2</v>
+        <v>1.7899999999999999E-2</v>
       </c>
       <c r="E22" s="8">
-        <v>734.05</v>
+        <v>732.24</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="42"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="40"/>
       <c r="C23" s="31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="7">
-        <v>1.37E-2</v>
+        <v>1.32E-2</v>
       </c>
       <c r="E23" s="8">
-        <v>5977</v>
+        <v>5844</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="C24" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="4">
-        <v>9.1999999999999998E-3</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>25</v>
-      </c>
       <c r="D24" s="7">
-        <v>9.1999999999999998E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="E24" s="8">
-        <v>171.15</v>
+        <v>155.53</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="4">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>27</v>
-      </c>
       <c r="D25" s="7">
-        <v>4.0000000000000001E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="E25" s="8">
-        <v>1388</v>
+        <v>1430</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="4">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="C26" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="4">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>29</v>
-      </c>
       <c r="D26" s="7">
-        <v>3.0000000000000001E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="E26" s="8">
-        <v>61.48</v>
+        <v>64.72</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1642,106 +1644,106 @@
       <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
+      <c r="A28" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="32">
-        <v>2.327</v>
-      </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
+      <c r="B29" s="37">
+        <v>2.319</v>
+      </c>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
       <c r="E29" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="38">
-        <v>-3.9699999999999999E-2</v>
-      </c>
-      <c r="G29" s="39"/>
+        <v>52</v>
+      </c>
+      <c r="F29" s="35">
+        <v>-3.3999999999999998E-3</v>
+      </c>
+      <c r="G29" s="36"/>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="F30" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="G30" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>1.4E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D31" s="7">
-        <v>1.4E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="E31" s="8">
-        <v>10.16</v>
+        <v>9.41</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="7">
+        <v>6.3E-3</v>
+      </c>
+      <c r="C32" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="7">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>32</v>
-      </c>
       <c r="D32" s="7">
-        <v>7.1000000000000004E-3</v>
+        <v>6.3E-3</v>
       </c>
       <c r="E32" s="8">
-        <v>115.71</v>
+        <v>104.51</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" s="41">
-        <v>1.55E-2</v>
+      <c r="A33" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="39">
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D33" s="7">
-        <v>7.6E-3</v>
+        <v>7.1999999999999998E-3</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>4</v>
@@ -1750,13 +1752,13 @@
       <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="40"/>
-      <c r="B34" s="41"/>
+      <c r="A34" s="38"/>
+      <c r="B34" s="39"/>
       <c r="C34" s="27" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D34" s="7">
-        <v>7.9000000000000008E-3</v>
+        <v>7.6E-3</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>4</v>
@@ -1765,35 +1767,35 @@
       <c r="G34" s="10"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="41">
-        <v>3.1099999999999999E-2</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>35</v>
+      <c r="A35" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="39">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>61</v>
       </c>
       <c r="D35" s="7">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="E35" s="8">
-        <v>1976.75</v>
+        <v>1949.83</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="40"/>
-      <c r="B36" s="41"/>
+      <c r="A36" s="38"/>
+      <c r="B36" s="39"/>
       <c r="C36" s="26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D36" s="7">
-        <v>3.0499999999999999E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="E36" s="8">
-        <v>366.9</v>
+        <v>387.25</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
@@ -1806,43 +1808,48 @@
       <c r="E37" s="17"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
+      <c r="A38" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
       <c r="D38" s="25"/>
       <c r="E38" s="25"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24"/>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1">
         <v>154004.837</v>
       </c>
       <c r="C40" s="9">
         <f>A2*B40</f>
-        <v>460628.46746700001</v>
+        <v>466942.66578400001</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A38:C38"/>
@@ -1859,11 +1866,6 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0" right="0" top="0.39370000000000011" bottom="0.39370000000000011" header="0" footer="0"/>

--- a/stock.xlsx
+++ b/stock.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\08.ubuntu_ws\ediedone.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09399B32-A8E7-417C-BCCF-8A1606ED5751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34779EB8-8421-46E1-8BDC-FFF8566F2E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{69258048-4F87-458D-9BA6-694171A7783B}"/>
   </bookViews>
@@ -131,9 +131,6 @@
     <t xml:space="preserve"> 通讯业务</t>
   </si>
   <si>
-    <t>哔哩哔哩</t>
-  </si>
-  <si>
     <t>其他</t>
   </si>
   <si>
@@ -379,6 +376,10 @@
     <t>思摩尔国际</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
+  <si>
+    <t>哔哩哔哩</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -526,7 +527,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,6 +574,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -703,7 +710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -782,22 +789,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="20" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -815,22 +816,34 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="17" fillId="9" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="9" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="20" fillId="9" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1198,30 +1211,30 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>39</v>
       </c>
       <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3">
-        <v>3.032</v>
+        <v>2.8580000000000001</v>
       </c>
       <c r="B2" s="4">
-        <v>1.38E-2</v>
+        <v>-5.74E-2</v>
       </c>
       <c r="C2" s="5">
-        <v>230.26</v>
-      </c>
-      <c r="D2" s="30">
+        <v>203.54</v>
+      </c>
+      <c r="D2" s="38">
         <v>0.72219999999999995</v>
       </c>
       <c r="E2" s="24"/>
@@ -1234,65 +1247,65 @@
       <c r="E3" s="24"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
+      <c r="A4" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="37">
-        <v>3.27</v>
-      </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
+      <c r="B5" s="27">
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
       <c r="E5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="33">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="G5" s="34"/>
+        <v>51</v>
+      </c>
+      <c r="F5" s="31">
+        <v>-6.8900000000000003E-2</v>
+      </c>
+      <c r="G5" s="32"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="29">
         <v>3.9600000000000003E-2</v>
       </c>
-      <c r="C7" s="28" t="s">
-        <v>60</v>
+      <c r="C7" s="39" t="s">
+        <v>59</v>
       </c>
       <c r="D7" s="7">
         <v>1.9800000000000002E-2</v>
@@ -1304,10 +1317,10 @@
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="42"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="28" t="s">
-        <v>59</v>
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="39" t="s">
+        <v>58</v>
       </c>
       <c r="D8" s="7">
         <v>1.0999999999999999E-2</v>
@@ -1319,10 +1332,10 @@
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="42"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="28" t="s">
-        <v>58</v>
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="39" t="s">
+        <v>57</v>
       </c>
       <c r="D9" s="7">
         <v>8.8000000000000005E-3</v>
@@ -1334,13 +1347,13 @@
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="29">
         <v>1.06E-2</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="40" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7">
@@ -1353,9 +1366,9 @@
       <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="42"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="31" t="s">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="40" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="7">
@@ -1374,7 +1387,7 @@
       <c r="B12" s="4">
         <v>6.1000000000000004E-3</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="40" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="7">
@@ -1393,7 +1406,7 @@
       <c r="B13" s="4">
         <v>4.8599999999999997E-2</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="40" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="7">
@@ -1406,14 +1419,14 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="40">
+      <c r="B14" s="29">
         <v>0.38219999999999998</v>
       </c>
-      <c r="C14" s="28" t="s">
-        <v>57</v>
+      <c r="C14" s="39" t="s">
+        <v>56</v>
       </c>
       <c r="D14" s="7">
         <v>0.1241</v>
@@ -1425,9 +1438,9 @@
       <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="38"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="31" t="s">
+      <c r="A15" s="35"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="40" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="7">
@@ -1440,9 +1453,9 @@
       <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="38"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="31" t="s">
+      <c r="A16" s="35"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="40" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="7">
@@ -1461,7 +1474,7 @@
       <c r="B17" s="4">
         <v>2.4899999999999999E-2</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="40" t="s">
         <v>14</v>
       </c>
       <c r="D17" s="7">
@@ -1474,14 +1487,14 @@
       <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="29">
         <v>4.2099999999999999E-2</v>
       </c>
-      <c r="C18" s="28" t="s">
-        <v>54</v>
+      <c r="C18" s="39" t="s">
+        <v>53</v>
       </c>
       <c r="D18" s="7">
         <v>3.1E-2</v>
@@ -1493,9 +1506,9 @@
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="41"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="31" t="s">
+      <c r="A19" s="37"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="40" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="7">
@@ -1514,7 +1527,7 @@
       <c r="B20" s="4">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="40" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="7">
@@ -1533,7 +1546,7 @@
       <c r="B21" s="4">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="40" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="7">
@@ -1546,14 +1559,14 @@
       <c r="G21" s="10"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="29">
         <v>3.1099999999999999E-2</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>62</v>
+      <c r="C22" s="41" t="s">
+        <v>61</v>
       </c>
       <c r="D22" s="7">
         <v>1.7899999999999999E-2</v>
@@ -1565,9 +1578,9 @@
       <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="41"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="31" t="s">
+      <c r="A23" s="37"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="40" t="s">
         <v>22</v>
       </c>
       <c r="D23" s="7">
@@ -1586,7 +1599,7 @@
       <c r="B24" s="4">
         <v>8.3000000000000001E-3</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="40" t="s">
         <v>24</v>
       </c>
       <c r="D24" s="7">
@@ -1605,7 +1618,7 @@
       <c r="B25" s="4">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="40" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="7">
@@ -1624,7 +1637,7 @@
       <c r="B26" s="4">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="40" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="7">
@@ -1644,54 +1657,54 @@
       <c r="E27" s="17"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
+      <c r="A28" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="37">
-        <v>2.319</v>
-      </c>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
+      <c r="B29" s="27">
+        <v>2.2789999999999999</v>
+      </c>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
       <c r="E29" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F29" s="35">
-        <v>-3.3999999999999998E-3</v>
-      </c>
-      <c r="G29" s="36"/>
+        <v>51</v>
+      </c>
+      <c r="F29" s="33">
+        <v>-1.7399999999999999E-2</v>
+      </c>
+      <c r="G29" s="34"/>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="E30" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="F30" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="G30" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1701,8 +1714,8 @@
       <c r="B31" s="7">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="C31" s="29" t="s">
-        <v>55</v>
+      <c r="C31" s="42" t="s">
+        <v>54</v>
       </c>
       <c r="D31" s="7">
         <v>1.2999999999999999E-2</v>
@@ -1721,10 +1734,10 @@
         <v>6.3E-3</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D32" s="7">
-        <v>6.3E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="E32" s="8">
         <v>104.51</v>
@@ -1733,14 +1746,14 @@
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="39">
+      <c r="A33" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="36">
         <v>1.4800000000000001E-2</v>
       </c>
-      <c r="C33" s="27" t="s">
-        <v>56</v>
+      <c r="C33" s="44" t="s">
+        <v>55</v>
       </c>
       <c r="D33" s="7">
         <v>7.1999999999999998E-3</v>
@@ -1752,10 +1765,10 @@
       <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="38"/>
-      <c r="B34" s="39"/>
-      <c r="C34" s="27" t="s">
-        <v>53</v>
+      <c r="A34" s="35"/>
+      <c r="B34" s="36"/>
+      <c r="C34" s="44" t="s">
+        <v>52</v>
       </c>
       <c r="D34" s="7">
         <v>7.6E-3</v>
@@ -1767,14 +1780,14 @@
       <c r="G34" s="10"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="39">
+      <c r="A35" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="36">
         <v>3.2599999999999997E-2</v>
       </c>
-      <c r="C35" s="29" t="s">
-        <v>61</v>
+      <c r="C35" s="42" t="s">
+        <v>60</v>
       </c>
       <c r="D35" s="7">
         <v>5.9999999999999995E-4</v>
@@ -1786,10 +1799,10 @@
       <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="38"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="26" t="s">
-        <v>34</v>
+      <c r="A36" s="35"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="43" t="s">
+        <v>33</v>
       </c>
       <c r="D36" s="7">
         <v>3.2000000000000001E-2</v>
@@ -1808,48 +1821,43 @@
       <c r="E37" s="17"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
+      <c r="A38" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
       <c r="D38" s="25"/>
       <c r="E38" s="25"/>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="C39" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="24"/>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" s="1">
         <v>154004.837</v>
       </c>
       <c r="C40" s="9">
         <f>A2*B40</f>
-        <v>466942.66578400001</v>
+        <v>440145.82414600003</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A28:G28"/>
     <mergeCell ref="A38:C38"/>
@@ -1866,6 +1874,11 @@
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0" right="0" top="0.39370000000000011" bottom="0.39370000000000011" header="0" footer="0"/>
